--- a/artfynd/A 657-2026 artfynd.xlsx
+++ b/artfynd/A 657-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1215,6 +1215,393 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131740813</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106160</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bovallen, Skultuna, Vstm, Bovallen, Skultuna, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>573283</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6623735</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skultuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131741217</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57090</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bovallen, Skultuna, Vstm, Bovallen, Skultuna, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>573193</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6623741</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skultuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På grusväg</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Öppen fastmark - med eller utan enstaka träd</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131741117</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57090</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bovallen, Skultuna, Vstm, Bovallen, Skultuna, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>573194</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6623742</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skultuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På grusväg</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Öppen fastmark - med eller utan enstaka träd</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 657-2026 artfynd.xlsx
+++ b/artfynd/A 657-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>131740813</v>
       </c>
       <c r="B7" t="n">
-        <v>106160</v>
+        <v>106166</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>131741217</v>
       </c>
       <c r="B8" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>131741117</v>
       </c>
       <c r="B9" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 657-2026 artfynd.xlsx
+++ b/artfynd/A 657-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>131740813</v>
       </c>
       <c r="B7" t="n">
-        <v>106166</v>
+        <v>106170</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>131741217</v>
       </c>
       <c r="B8" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>131741117</v>
       </c>
       <c r="B9" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 657-2026 artfynd.xlsx
+++ b/artfynd/A 657-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>131740813</v>
       </c>
       <c r="B7" t="n">
-        <v>106170</v>
+        <v>106175</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>131741217</v>
       </c>
       <c r="B8" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>131741117</v>
       </c>
       <c r="B9" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 657-2026 artfynd.xlsx
+++ b/artfynd/A 657-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>131740813</v>
       </c>
       <c r="B7" t="n">
-        <v>106219</v>
+        <v>106222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 657-2026 artfynd.xlsx
+++ b/artfynd/A 657-2026 artfynd.xlsx
@@ -1220,7 +1220,7 @@
         <v>131740813</v>
       </c>
       <c r="B7" t="n">
-        <v>106222</v>
+        <v>106230</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>131741217</v>
       </c>
       <c r="B8" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>131741117</v>
       </c>
       <c r="B9" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 657-2026 artfynd.xlsx
+++ b/artfynd/A 657-2026 artfynd.xlsx
@@ -1341,7 +1341,7 @@
         <v>131741217</v>
       </c>
       <c r="B8" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>131741117</v>
       </c>
       <c r="B9" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 657-2026 artfynd.xlsx
+++ b/artfynd/A 657-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114257167</v>
+        <v>114257166</v>
       </c>
       <c r="B2" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573148</v>
+        <v>573084</v>
       </c>
       <c r="R2" t="n">
-        <v>6623749</v>
+        <v>6623780</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126216378</v>
+        <v>114257167</v>
       </c>
       <c r="B3" t="n">
-        <v>98281</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,41 +795,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223597</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövkärret N, Vstm</t>
+          <t>Kranshällarna, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573286</v>
+        <v>573148</v>
       </c>
       <c r="R3" t="n">
-        <v>6623712</v>
+        <v>6623749</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,12 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2023-04-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2023-04-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,34 +871,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Väg-dikesren</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Samuel Holdar</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Johan Frölinghaus</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>PÖN0100 fågelinventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126216447</v>
+        <v>126216658</v>
       </c>
       <c r="B4" t="n">
-        <v>98281</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,27 +904,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223597</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -935,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573223</v>
+        <v>573207</v>
       </c>
       <c r="R4" t="n">
-        <v>6623756</v>
+        <v>6623635</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,13 +984,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Väg-dikesren</t>
+          <t>Hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1003,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126216401</v>
+        <v>131741117</v>
       </c>
       <c r="B5" t="n">
-        <v>97239</v>
+        <v>57162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,41 +1018,53 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lövkärret N, Vstm</t>
+          <t>Bovallen, Skultuna, Vstm, Bovallen, Skultuna, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573286</v>
+        <v>573194</v>
       </c>
       <c r="R5" t="n">
-        <v>6623712</v>
+        <v>6623742</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1072,12 +1088,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På grusväg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,34 +1117,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Väg-dikesren</t>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Öppen fastmark - med eller utan enstaka träd</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126216405</v>
+        <v>131741217</v>
       </c>
       <c r="B6" t="n">
-        <v>97242</v>
+        <v>57162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1121,41 +1151,53 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lövkärret N, Vstm</t>
+          <t>Bovallen, Skultuna, Vstm, Bovallen, Skultuna, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573286</v>
+        <v>573193</v>
       </c>
       <c r="R6" t="n">
-        <v>6623712</v>
+        <v>6623741</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1179,12 +1221,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På grusväg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,34 +1250,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Väg-dikesren</t>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Öppen fastmark - med eller utan enstaka träd</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131740813</v>
+        <v>131741444</v>
       </c>
       <c r="B7" t="n">
-        <v>106230</v>
+        <v>57162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1228,43 +1284,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bovallen, Skultuna, Vstm, Bovallen, Skultuna, Vstm, Vstm</t>
+          <t>Bovallen, Skultuna, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573283</v>
+        <v>573150</v>
       </c>
       <c r="R7" t="n">
-        <v>6623735</v>
+        <v>6623664</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1296,7 +1359,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1306,7 +1369,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spillningshög på häll</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,11 +1385,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1338,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131741217</v>
+        <v>131741713</v>
       </c>
       <c r="B8" t="n">
-        <v>57141</v>
+        <v>57162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,14 +1430,10 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1389,10 +1448,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573193</v>
+        <v>573187</v>
       </c>
       <c r="R8" t="n">
-        <v>6623741</v>
+        <v>6623648</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1424,7 +1483,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,12 +1493,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På grusväg</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,11 +1504,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Öppen fastmark - med eller utan enstaka träd</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1471,10 +1520,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131741117</v>
+        <v>128194072</v>
       </c>
       <c r="B9" t="n">
-        <v>57141</v>
+        <v>58790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,53 +1531,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>208245</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bovallen, Skultuna, Vstm, Bovallen, Skultuna, Vstm, Vstm</t>
+          <t>Lövkärret, Lövkärret, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573194</v>
+        <v>573119</v>
       </c>
       <c r="R9" t="n">
-        <v>6623742</v>
+        <v>6623695</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,27 +1594,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På grusväg</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,11 +1620,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Öppen fastmark - med eller utan enstaka träd</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1601,6 +1633,555 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131740813</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bovallen, Skultuna, Vstm, Bovallen, Skultuna, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>573283</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6623735</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skultuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126216401</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lövkärret N, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>573286</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6623712</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skultuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Väg-dikesren</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126216405</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lövkärret N, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>573286</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6623712</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skultuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Väg-dikesren</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126216378</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lövkärret N, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>573286</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6623712</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skultuna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Väg-dikesren</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126216447</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lövkärret N, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>573223</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6623756</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skultuna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Väg-dikesren</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 657-2026 artfynd.xlsx
+++ b/artfynd/A 657-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257166</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
           <t>PÖN0100 fågelinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114257167</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126216658</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1137,6 +1157,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131741117</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1270,6 +1295,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131741217</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1398,6 +1428,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131741444</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1517,6 +1552,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131741713</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1633,6 +1673,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128194072</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1754,6 +1799,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740813</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1861,6 +1911,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126216401</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1968,6 +2023,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126216405</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2075,6 +2135,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126216378</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2182,8 +2247,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126216447</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>